--- a/output/laminas_comunales/comunal_o_ocup_a_2022_metropolitana.xlsx
+++ b/output/laminas_comunales/comunal_o_ocup_a_2022_metropolitana.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C52"/>
+  <dimension ref="A1:C379"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -375,16 +375,16 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>13101</t>
+          <t>13120</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Santiago</t>
+          <t>Ñuñoa</t>
         </is>
       </c>
       <c r="C2">
-        <v>50.2870677923521</v>
+        <v>70.23825928784041</v>
       </c>
     </row>
     <row r="3">
@@ -399,742 +399,5647 @@
         </is>
       </c>
       <c r="C3">
-        <v>49.9998627161877</v>
+        <v>69.52136061552351</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>13120</t>
+          <t>13132</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Ñuñoa</t>
+          <t>Vitacura</t>
         </is>
       </c>
       <c r="C4">
-        <v>48.4464224329258</v>
+        <v>69.3960990247562</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>13123</t>
+          <t>13114</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Providencia</t>
+          <t>Las Condes</t>
         </is>
       </c>
       <c r="C5">
-        <v>48.1299286337459</v>
+        <v>68.9025387967412</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>13125</t>
+          <t>13123</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Quilicura</t>
+          <t>Providencia</t>
         </is>
       </c>
       <c r="C6">
-        <v>47.1320590180437</v>
+        <v>67.1000375156854</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>13108</t>
+          <t>13115</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Independencia</t>
+          <t>Lo Barnechea</t>
         </is>
       </c>
       <c r="C7">
-        <v>46.0431909915083</v>
+        <v>64.7625468507176</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>13106</t>
+          <t>13118</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Estación Central</t>
+          <t>Macul</t>
         </is>
       </c>
       <c r="C8">
-        <v>44.7536491177945</v>
+        <v>64.0594956180298</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>13114</t>
+          <t>13107</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Las Condes</t>
+          <t>Huechuraba</t>
         </is>
       </c>
       <c r="C9">
-        <v>44.7443652529455</v>
+        <v>62.9714783758603</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>13302</t>
+          <t>13101</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Lampa</t>
+          <t>Santiago</t>
         </is>
       </c>
       <c r="C10">
-        <v>44.7303668618483</v>
+        <v>62.8681042334957</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>13301</t>
+          <t>13120</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Colina</t>
+          <t>Ñuñoa</t>
         </is>
       </c>
       <c r="C11">
-        <v>44.6734621583325</v>
+        <v>62.4544582154126</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>13604</t>
+          <t>13125</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Padre Hurtado</t>
+          <t>Quilicura</t>
         </is>
       </c>
       <c r="C12">
-        <v>43.7738182435804</v>
+        <v>62.3971674999502</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>13107</t>
+          <t>13110</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Huechuraba</t>
+          <t>La Florida</t>
         </is>
       </c>
       <c r="C13">
-        <v>43.4254239009036</v>
+        <v>62.2316785134189</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>13126</t>
+          <t>13119</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Quinta Normal</t>
+          <t>Maipú</t>
         </is>
       </c>
       <c r="C14">
-        <v>43.3535139839155</v>
+        <v>62.2064903658632</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>13115</t>
+          <t>13123</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Lo Barnechea</t>
+          <t>Providencia</t>
         </is>
       </c>
       <c r="C15">
-        <v>43.3433495626372</v>
+        <v>62.0703504133338</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>13118</t>
+          <t>13114</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Macul</t>
+          <t>Las Condes</t>
         </is>
       </c>
       <c r="C16">
-        <v>42.9827721435868</v>
+        <v>62.0516139565258</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>13402</t>
+          <t>13113</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Buin</t>
+          <t>La Reina</t>
         </is>
       </c>
       <c r="C17">
-        <v>42.8525884867587</v>
+        <v>61.9549509144366</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>13132</t>
+          <t>13115</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Vitacura</t>
+          <t>Lo Barnechea</t>
         </is>
       </c>
       <c r="C18">
-        <v>42.6035455972702</v>
+        <v>61.7199114104548</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>13119</t>
+          <t>13301</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Maipú</t>
+          <t>Colina</t>
         </is>
       </c>
       <c r="C19">
-        <v>42.4388550602108</v>
+        <v>61.6213252351428</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>13124</t>
+          <t>13109</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Pudahuel</t>
+          <t>La Cisterna</t>
         </is>
       </c>
       <c r="C20">
-        <v>42.3299140850619</v>
+        <v>61.322584873509</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>13403</t>
+          <t>13101</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Calera de Tango</t>
+          <t>Santiago</t>
         </is>
       </c>
       <c r="C21">
-        <v>42.0878781211035</v>
+        <v>61.2542373648025</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>13201</t>
+          <t>13604</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Puente Alto</t>
+          <t>Padre Hurtado</t>
         </is>
       </c>
       <c r="C22">
-        <v>42.0499760341412</v>
+        <v>61.2378101218582</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>13109</t>
+          <t>13302</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>La Cisterna</t>
+          <t>Lampa</t>
         </is>
       </c>
       <c r="C23">
-        <v>41.6289232511235</v>
+        <v>61.0733205218152</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>13110</t>
+          <t>13130</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>La Florida</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="C24">
-        <v>41.3743475510649</v>
+        <v>60.822457353809</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>13102</t>
+          <t>13402</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Cerrillos</t>
+          <t>Buin</t>
         </is>
       </c>
       <c r="C25">
-        <v>41.3190540572594</v>
+        <v>60.7986838169309</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>13128</t>
+          <t>13132</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Renca</t>
+          <t>Vitacura</t>
         </is>
       </c>
       <c r="C26">
-        <v>41.2680153760581</v>
+        <v>60.7706551013942</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>13401</t>
+          <t>13126</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>San Bernardo</t>
+          <t>Quinta Normal</t>
         </is>
       </c>
       <c r="C27">
-        <v>40.7236140904737</v>
+        <v>60.665454794226</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>13122</t>
+          <t>13108</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Peñalolén</t>
+          <t>Independencia</t>
         </is>
       </c>
       <c r="C28">
-        <v>40.7231514668791</v>
+        <v>60.1023070585004</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>13113</t>
+          <t>13124</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>La Reina</t>
+          <t>Pudahuel</t>
         </is>
       </c>
       <c r="C29">
-        <v>40.2626644827338</v>
+        <v>60.0580156287</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>13605</t>
+          <t>13201</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Peñaflor</t>
+          <t>Puente Alto</t>
         </is>
       </c>
       <c r="C30">
-        <v>40.0351447197978</v>
+        <v>59.9456437253151</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>13127</t>
+          <t>13106</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Estación Central</t>
         </is>
       </c>
       <c r="C31">
-        <v>39.7963961674573</v>
+        <v>59.7924829912081</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>13202</t>
+          <t>13113</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Pirque</t>
+          <t>La Reina</t>
         </is>
       </c>
       <c r="C32">
-        <v>39.3982742178254</v>
+        <v>59.4607507934003</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>13104</t>
+          <t>13605</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Conchalí</t>
+          <t>Peñaflor</t>
         </is>
       </c>
       <c r="C33">
-        <v>39.0449250082952</v>
+        <v>58.7012344515643</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>13117</t>
+          <t>13125</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Lo Prado</t>
+          <t>Quilicura</t>
         </is>
       </c>
       <c r="C34">
-        <v>38.7635871230224</v>
+        <v>58.6900892177882</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>13601</t>
+          <t>13102</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Talagante</t>
+          <t>Cerrillos</t>
         </is>
       </c>
       <c r="C35">
-        <v>38.729830851976</v>
+        <v>58.5990387219063</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>13502</t>
+          <t>13122</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Alhué</t>
+          <t>Peñalolén</t>
         </is>
       </c>
       <c r="C36">
-        <v>38.6516279748868</v>
+        <v>58.0565841427399</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>13404</t>
+          <t>13128</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Paine</t>
+          <t>Renca</t>
         </is>
       </c>
       <c r="C37">
-        <v>38.4071177160735</v>
+        <v>57.8820598835874</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>13103</t>
+          <t>13601</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Cerro Navia</t>
+          <t>Talagante</t>
         </is>
       </c>
       <c r="C38">
-        <v>38.3663670617563</v>
+        <v>57.862486602358</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>13129</t>
+          <t>13403</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>San Joaquín</t>
+          <t>Calera de Tango</t>
         </is>
       </c>
       <c r="C39">
-        <v>38.1839090964479</v>
+        <v>57.5294137942932</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>13603</t>
+          <t>13107</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Isla de Maipo</t>
+          <t>Huechuraba</t>
         </is>
       </c>
       <c r="C40">
-        <v>38.1076766797272</v>
+        <v>57.4315934523539</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>13116</t>
+          <t>13101</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Lo Espejo</t>
+          <t>Santiago</t>
         </is>
       </c>
       <c r="C41">
-        <v>37.248023715415</v>
+        <v>57.2843760201929</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>13602</t>
+          <t>13401</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>El Monte</t>
+          <t>San Bernardo</t>
         </is>
       </c>
       <c r="C42">
-        <v>37.1882967477147</v>
+        <v>56.9837687988154</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>13111</t>
+          <t>13202</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>La Granja</t>
+          <t>Pirque</t>
         </is>
       </c>
       <c r="C43">
-        <v>36.4629778764249</v>
+        <v>56.8049358897062</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>13105</t>
+          <t>13117</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>El Bosque</t>
+          <t>Lo Prado</t>
         </is>
       </c>
       <c r="C44">
-        <v>36.3576761635898</v>
+        <v>56.5658631253107</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>13112</t>
+          <t>13104</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>La Pintana</t>
+          <t>Conchalí</t>
         </is>
       </c>
       <c r="C45">
-        <v>36.0218406407262</v>
+        <v>56.466468883676</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>13131</t>
+          <t>13129</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>San Ramón</t>
+          <t>San Joaquín</t>
         </is>
       </c>
       <c r="C46">
-        <v>35.6509139346636</v>
+        <v>56.4174429148463</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>13203</t>
+          <t>13118</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>San José de Maipo</t>
+          <t>Macul</t>
         </is>
       </c>
       <c r="C47">
-        <v>35.6471066116735</v>
+        <v>56.2594190274725</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>13501</t>
+          <t>13601</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Melipilla</t>
+          <t>Talagante</t>
         </is>
       </c>
       <c r="C48">
-        <v>35.5083465257172</v>
+        <v>56.1887425194079</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>13121</t>
+          <t>13119</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Pedro Aguirre Cerda</t>
+          <t>Maipú</t>
         </is>
       </c>
       <c r="C49">
-        <v>35.4562726892324</v>
+        <v>56.1655084015942</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>13503</t>
+          <t>13301</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Curacaví</t>
+          <t>Colina</t>
         </is>
       </c>
       <c r="C50">
-        <v>35.0462871882309</v>
+        <v>55.9929618578101</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>13504</t>
+          <t>13108</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>María Pinto</t>
+          <t>Independencia</t>
         </is>
       </c>
       <c r="C51">
-        <v>34.9475045648204</v>
+        <v>55.9276626850815</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
+          <t>13603</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Isla de Maipo</t>
+        </is>
+      </c>
+      <c r="C52">
+        <v>55.6355995797689</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>13502</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Alhué</t>
+        </is>
+      </c>
+      <c r="C53">
+        <v>55.5902430902431</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>13404</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Paine</t>
+        </is>
+      </c>
+      <c r="C54">
+        <v>55.5743180895434</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>13110</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>La Florida</t>
+        </is>
+      </c>
+      <c r="C55">
+        <v>55.5217972885487</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>13127</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Recoleta</t>
+        </is>
+      </c>
+      <c r="C56">
+        <v>55.3721079433818</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>13126</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Quinta Normal</t>
+        </is>
+      </c>
+      <c r="C57">
+        <v>54.91820287294</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>13101</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Santiago</t>
+        </is>
+      </c>
+      <c r="C58">
+        <v>54.879226984425</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>13102</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Cerrillos</t>
+        </is>
+      </c>
+      <c r="C59">
+        <v>54.8439694962874</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>13103</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Cerro Navia</t>
+        </is>
+      </c>
+      <c r="C60">
+        <v>54.6905446285351</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>13109</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>La Cisterna</t>
+        </is>
+      </c>
+      <c r="C61">
+        <v>54.6675156414374</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>13125</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Quilicura</t>
+        </is>
+      </c>
+      <c r="C62">
+        <v>54.3165524964035</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>13122</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Peñalolén</t>
+        </is>
+      </c>
+      <c r="C63">
+        <v>53.9664582038533</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>13602</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>El Monte</t>
+        </is>
+      </c>
+      <c r="C64">
+        <v>53.7732396428049</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>13106</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Estación Central</t>
+        </is>
+      </c>
+      <c r="C65">
+        <v>53.5788503435562</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>13121</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Pedro Aguirre Cerda</t>
+        </is>
+      </c>
+      <c r="C66">
+        <v>53.5655022149113</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>13130</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>San Miguel</t>
+        </is>
+      </c>
+      <c r="C67">
+        <v>53.5498642167909</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>13111</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>La Granja</t>
+        </is>
+      </c>
+      <c r="C68">
+        <v>53.4919211172154</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>13105</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>El Bosque</t>
+        </is>
+      </c>
+      <c r="C69">
+        <v>53.4144773275514</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>13201</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Puente Alto</t>
+        </is>
+      </c>
+      <c r="C70">
+        <v>53.3464566929134</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>13124</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Pudahuel</t>
+        </is>
+      </c>
+      <c r="C71">
+        <v>53.2419538698407</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>13116</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Lo Espejo</t>
+        </is>
+      </c>
+      <c r="C72">
+        <v>53.1291841077897</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>13101</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Santiago</t>
+        </is>
+      </c>
+      <c r="C73">
+        <v>53.1215068186899</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>13403</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Calera de Tango</t>
+        </is>
+      </c>
+      <c r="C74">
+        <v>52.9475523003746</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>13120</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Ñuñoa</t>
+        </is>
+      </c>
+      <c r="C75">
+        <v>52.7222307445068</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>13501</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Melipilla</t>
+        </is>
+      </c>
+      <c r="C76">
+        <v>52.1919117946214</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>13128</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Renca</t>
+        </is>
+      </c>
+      <c r="C77">
+        <v>52.1539299775028</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>13131</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>San Ramón</t>
+        </is>
+      </c>
+      <c r="C78">
+        <v>52.1531719681554</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>13503</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Curacaví</t>
+        </is>
+      </c>
+      <c r="C79">
+        <v>51.9847990000403</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>13203</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>San José de Maipo</t>
+        </is>
+      </c>
+      <c r="C80">
+        <v>51.9635234769111</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>13504</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>María Pinto</t>
+        </is>
+      </c>
+      <c r="C81">
+        <v>51.9453132404511</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>13501</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Melipilla</t>
+        </is>
+      </c>
+      <c r="C82">
+        <v>51.8867569986812</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>13123</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Providencia</t>
+        </is>
+      </c>
+      <c r="C83">
+        <v>51.8025180251803</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>13605</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Peñaflor</t>
+        </is>
+      </c>
+      <c r="C84">
+        <v>51.7405172117336</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>13117</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Lo Prado</t>
+        </is>
+      </c>
+      <c r="C85">
+        <v>51.6982761511889</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>13402</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Buin</t>
+        </is>
+      </c>
+      <c r="C86">
+        <v>51.6501411885509</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>13302</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Lampa</t>
+        </is>
+      </c>
+      <c r="C87">
+        <v>51.5655678597183</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>13127</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Recoleta</t>
+        </is>
+      </c>
+      <c r="C88">
+        <v>51.4249699394748</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>13604</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Padre Hurtado</t>
+        </is>
+      </c>
+      <c r="C89">
+        <v>51.3879116239797</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>13401</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>San Bernardo</t>
+        </is>
+      </c>
+      <c r="C90">
+        <v>51.3082816849245</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>13104</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Conchalí</t>
+        </is>
+      </c>
+      <c r="C91">
+        <v>51.2509154634861</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>13604</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Padre Hurtado</t>
+        </is>
+      </c>
+      <c r="C92">
+        <v>51.1742592240596</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>13302</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Lampa</t>
+        </is>
+      </c>
+      <c r="C93">
+        <v>50.5586212412028</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>13101</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Santiago</t>
+        </is>
+      </c>
+      <c r="C94">
+        <v>50.2870677923521</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>13129</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>San Joaquín</t>
+        </is>
+      </c>
+      <c r="C95">
+        <v>50.1088300336067</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>13130</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>San Miguel</t>
+        </is>
+      </c>
+      <c r="C96">
+        <v>49.9998627161877</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>13601</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Talagante</t>
+        </is>
+      </c>
+      <c r="C97">
+        <v>49.8110151187905</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>13301</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Colina</t>
+        </is>
+      </c>
+      <c r="C98">
+        <v>49.6745044171515</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>13108</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Independencia</t>
+        </is>
+      </c>
+      <c r="C99">
+        <v>49.6374127321026</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>13112</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>La Pintana</t>
+        </is>
+      </c>
+      <c r="C100">
+        <v>49.2643611766873</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>13601</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Talagante</t>
+        </is>
+      </c>
+      <c r="C101">
+        <v>49.138159639353</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>13106</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Estación Central</t>
+        </is>
+      </c>
+      <c r="C102">
+        <v>49.1291514268166</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>13119</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Maipú</t>
+        </is>
+      </c>
+      <c r="C103">
+        <v>49.1056552974263</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>13402</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Buin</t>
+        </is>
+      </c>
+      <c r="C104">
+        <v>48.9662881554773</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>13114</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Las Condes</t>
+        </is>
+      </c>
+      <c r="C105">
+        <v>48.883932179282</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>13201</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Puente Alto</t>
+        </is>
+      </c>
+      <c r="C106">
+        <v>48.8008307925454</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>13124</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Pudahuel</t>
+        </is>
+      </c>
+      <c r="C107">
+        <v>48.6762674675488</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>13203</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>San José de Maipo</t>
+        </is>
+      </c>
+      <c r="C108">
+        <v>48.6397185032612</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>13120</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Ñuñoa</t>
+        </is>
+      </c>
+      <c r="C109">
+        <v>48.4464224329258</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>13107</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Huechuraba</t>
+        </is>
+      </c>
+      <c r="C110">
+        <v>48.4140672175762</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>13128</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Renca</t>
+        </is>
+      </c>
+      <c r="C111">
+        <v>48.1854338610021</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>13123</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Providencia</t>
+        </is>
+      </c>
+      <c r="C112">
+        <v>48.1299286337459</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>13126</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Quinta Normal</t>
+        </is>
+      </c>
+      <c r="C113">
+        <v>48.0794491590144</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>13202</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Pirque</t>
+        </is>
+      </c>
+      <c r="C114">
+        <v>48.0676840469125</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>13401</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>San Bernardo</t>
+        </is>
+      </c>
+      <c r="C115">
+        <v>48.0483276526173</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>13404</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Paine</t>
+        </is>
+      </c>
+      <c r="C116">
+        <v>48.0224679423514</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>13101</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Santiago</t>
+        </is>
+      </c>
+      <c r="C117">
+        <v>47.8960191608854</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>13102</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Cerrillos</t>
+        </is>
+      </c>
+      <c r="C118">
+        <v>47.8358116125081</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>13101</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Santiago</t>
+        </is>
+      </c>
+      <c r="C119">
+        <v>47.4773620908515</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>13103</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Cerro Navia</t>
+        </is>
+      </c>
+      <c r="C120">
+        <v>47.4565588737704</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>13605</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Peñaflor</t>
+        </is>
+      </c>
+      <c r="C121">
+        <v>47.3757731690836</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>13502</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Alhué</t>
+        </is>
+      </c>
+      <c r="C122">
+        <v>47.3328831870358</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>13502</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Alhué</t>
+        </is>
+      </c>
+      <c r="C123">
+        <v>47.3101878752663</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>13132</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Vitacura</t>
+        </is>
+      </c>
+      <c r="C124">
+        <v>47.2424024886336</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>13121</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Pedro Aguirre Cerda</t>
+        </is>
+      </c>
+      <c r="C125">
+        <v>47.235735815134</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>13603</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Isla de Maipo</t>
+        </is>
+      </c>
+      <c r="C126">
+        <v>47.1734767943299</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>13125</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Quilicura</t>
+        </is>
+      </c>
+      <c r="C127">
+        <v>47.1320590180437</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>13601</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Talagante</t>
+        </is>
+      </c>
+      <c r="C128">
+        <v>47.1168759507263</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>13118</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Macul</t>
+        </is>
+      </c>
+      <c r="C129">
+        <v>46.9712381171714</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>13110</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>La Florida</t>
+        </is>
+      </c>
+      <c r="C130">
+        <v>46.934127848756</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>13105</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>El Bosque</t>
+        </is>
+      </c>
+      <c r="C131">
+        <v>46.8578243855252</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>13130</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>San Miguel</t>
+        </is>
+      </c>
+      <c r="C132">
+        <v>46.7854545644793</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>13115</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Lo Barnechea</t>
+        </is>
+      </c>
+      <c r="C133">
+        <v>46.7792156681174</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>13403</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Calera de Tango</t>
+        </is>
+      </c>
+      <c r="C134">
+        <v>46.7394589021615</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>13111</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>La Granja</t>
+        </is>
+      </c>
+      <c r="C135">
+        <v>46.6293158422155</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>13109</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>La Cisterna</t>
+        </is>
+      </c>
+      <c r="C136">
+        <v>46.5350477457283</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>13108</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Independencia</t>
+        </is>
+      </c>
+      <c r="C137">
+        <v>46.0431909915083</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>13602</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>El Monte</t>
+        </is>
+      </c>
+      <c r="C138">
+        <v>45.8845374746793</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>13603</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Isla de Maipo</t>
+        </is>
+      </c>
+      <c r="C139">
+        <v>45.6003821734574</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>13116</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Lo Espejo</t>
+        </is>
+      </c>
+      <c r="C140">
+        <v>45.4135101010101</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>13601</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Talagante</t>
+        </is>
+      </c>
+      <c r="C141">
+        <v>45.3733518536057</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>13116</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Lo Espejo</t>
+        </is>
+      </c>
+      <c r="C142">
+        <v>45.2012342874451</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>13101</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Santiago</t>
+        </is>
+      </c>
+      <c r="C143">
+        <v>45.0595952958238</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>13131</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>San Ramón</t>
+        </is>
+      </c>
+      <c r="C144">
+        <v>44.9432404540764</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>13117</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Lo Prado</t>
+        </is>
+      </c>
+      <c r="C145">
+        <v>44.8678744271703</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>13120</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Ñuñoa</t>
+        </is>
+      </c>
+      <c r="C146">
+        <v>44.8495253018711</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>13122</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Peñalolén</t>
+        </is>
+      </c>
+      <c r="C147">
+        <v>44.827512368266</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>13103</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Cerro Navia</t>
+        </is>
+      </c>
+      <c r="C148">
+        <v>44.7920444406067</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>13504</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>María Pinto</t>
+        </is>
+      </c>
+      <c r="C149">
+        <v>44.7652657469789</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>13106</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Estación Central</t>
+        </is>
+      </c>
+      <c r="C150">
+        <v>44.7536491177945</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>13114</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Las Condes</t>
+        </is>
+      </c>
+      <c r="C151">
+        <v>44.7443652529455</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>13302</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Lampa</t>
+        </is>
+      </c>
+      <c r="C152">
+        <v>44.7303668618483</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>13123</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Providencia</t>
+        </is>
+      </c>
+      <c r="C153">
+        <v>44.6941524817221</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>13104</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Conchalí</t>
+        </is>
+      </c>
+      <c r="C154">
+        <v>44.6743399588415</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>13301</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Colina</t>
+        </is>
+      </c>
+      <c r="C155">
+        <v>44.6734621583325</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>13202</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Pirque</t>
+        </is>
+      </c>
+      <c r="C156">
+        <v>44.6720269497235</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>13503</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Curacaví</t>
+        </is>
+      </c>
+      <c r="C157">
+        <v>44.5936494614631</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>13112</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>La Pintana</t>
+        </is>
+      </c>
+      <c r="C158">
+        <v>44.4454878392337</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>13404</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Paine</t>
+        </is>
+      </c>
+      <c r="C159">
+        <v>44.373504831143</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>13127</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Recoleta</t>
+        </is>
+      </c>
+      <c r="C160">
+        <v>44.2993034193589</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>13501</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Melipilla</t>
+        </is>
+      </c>
+      <c r="C161">
+        <v>44.1775352675007</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>13501</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Melipilla</t>
+        </is>
+      </c>
+      <c r="C162">
+        <v>43.8898483255744</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>13604</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Padre Hurtado</t>
+        </is>
+      </c>
+      <c r="C163">
+        <v>43.7738182435804</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
           <t>13505</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B164" t="inlineStr">
         <is>
           <t>San Pedro</t>
         </is>
       </c>
-      <c r="C52">
+      <c r="C164">
+        <v>43.6029962546816</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>13602</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>El Monte</t>
+        </is>
+      </c>
+      <c r="C165">
+        <v>43.5159407737359</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>13107</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Huechuraba</t>
+        </is>
+      </c>
+      <c r="C166">
+        <v>43.4254239009036</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>13126</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Quinta Normal</t>
+        </is>
+      </c>
+      <c r="C167">
+        <v>43.3535139839155</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>13115</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Lo Barnechea</t>
+        </is>
+      </c>
+      <c r="C168">
+        <v>43.3433495626372</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>13129</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>San Joaquín</t>
+        </is>
+      </c>
+      <c r="C169">
+        <v>43.2066654225374</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>13113</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>La Reina</t>
+        </is>
+      </c>
+      <c r="C170">
+        <v>43.1441269328741</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>13112</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>La Pintana</t>
+        </is>
+      </c>
+      <c r="C171">
+        <v>43.0925046653911</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>13118</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Macul</t>
+        </is>
+      </c>
+      <c r="C172">
+        <v>42.9827721435868</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>13402</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Buin</t>
+        </is>
+      </c>
+      <c r="C173">
+        <v>42.8525884867587</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>13105</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>El Bosque</t>
+        </is>
+      </c>
+      <c r="C174">
+        <v>42.7846737218783</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>13101</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Santiago</t>
+        </is>
+      </c>
+      <c r="C175">
+        <v>42.7728314238953</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>13132</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Vitacura</t>
+        </is>
+      </c>
+      <c r="C176">
+        <v>42.6035455972702</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>13111</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>La Granja</t>
+        </is>
+      </c>
+      <c r="C177">
+        <v>42.5972851578027</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>13108</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Independencia</t>
+        </is>
+      </c>
+      <c r="C178">
+        <v>42.5275987909412</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>13119</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Maipú</t>
+        </is>
+      </c>
+      <c r="C179">
+        <v>42.4388550602108</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>13124</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Pudahuel</t>
+        </is>
+      </c>
+      <c r="C180">
+        <v>42.3299140850619</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>13106</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Estación Central</t>
+        </is>
+      </c>
+      <c r="C181">
+        <v>42.2852127798629</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>13403</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Calera de Tango</t>
+        </is>
+      </c>
+      <c r="C182">
+        <v>42.0878781211035</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>13201</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Puente Alto</t>
+        </is>
+      </c>
+      <c r="C183">
+        <v>42.0499760341412</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>13108</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Independencia</t>
+        </is>
+      </c>
+      <c r="C184">
+        <v>41.9940194475518</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>13501</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Melipilla</t>
+        </is>
+      </c>
+      <c r="C185">
+        <v>41.8905785010235</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>13131</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>San Ramón</t>
+        </is>
+      </c>
+      <c r="C186">
+        <v>41.8713139106913</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>13109</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>La Cisterna</t>
+        </is>
+      </c>
+      <c r="C187">
+        <v>41.6289232511235</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>13121</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Pedro Aguirre Cerda</t>
+        </is>
+      </c>
+      <c r="C188">
+        <v>41.4592248347367</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>13110</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>La Florida</t>
+        </is>
+      </c>
+      <c r="C189">
+        <v>41.3743475510649</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>13102</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Cerrillos</t>
+        </is>
+      </c>
+      <c r="C190">
+        <v>41.3190540572594</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>13128</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Renca</t>
+        </is>
+      </c>
+      <c r="C191">
+        <v>41.2680153760581</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>13501</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Melipilla</t>
+        </is>
+      </c>
+      <c r="C192">
+        <v>41.0495402507448</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>13114</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Las Condes</t>
+        </is>
+      </c>
+      <c r="C193">
+        <v>41.0270645553024</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>13401</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>San Bernardo</t>
+        </is>
+      </c>
+      <c r="C194">
+        <v>40.7236140904737</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>13122</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Peñalolén</t>
+        </is>
+      </c>
+      <c r="C195">
+        <v>40.7231514668791</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>13106</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Estación Central</t>
+        </is>
+      </c>
+      <c r="C196">
+        <v>40.4692822425377</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>13504</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>María Pinto</t>
+        </is>
+      </c>
+      <c r="C197">
+        <v>40.2886172875865</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>13113</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>La Reina</t>
+        </is>
+      </c>
+      <c r="C198">
+        <v>40.2626644827338</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>13125</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Quilicura</t>
+        </is>
+      </c>
+      <c r="C199">
+        <v>40.2415650033633</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>13130</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>San Miguel</t>
+        </is>
+      </c>
+      <c r="C200">
+        <v>40.1355732961298</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>13115</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Lo Barnechea</t>
+        </is>
+      </c>
+      <c r="C201">
+        <v>40.0690169950214</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>13605</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Peñaflor</t>
+        </is>
+      </c>
+      <c r="C202">
+        <v>40.0351447197978</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>13601</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Talagante</t>
+        </is>
+      </c>
+      <c r="C203">
+        <v>40.0259621182914</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>13127</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Recoleta</t>
+        </is>
+      </c>
+      <c r="C204">
+        <v>39.7963961674573</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>13203</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>San José de Maipo</t>
+        </is>
+      </c>
+      <c r="C205">
+        <v>39.6500987624461</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>13301</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Colina</t>
+        </is>
+      </c>
+      <c r="C206">
+        <v>39.6323385677983</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>13503</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Curacaví</t>
+        </is>
+      </c>
+      <c r="C207">
+        <v>39.5821096826122</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>13126</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Quinta Normal</t>
+        </is>
+      </c>
+      <c r="C208">
+        <v>39.5143721246139</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>13202</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Pirque</t>
+        </is>
+      </c>
+      <c r="C209">
+        <v>39.3982742178254</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>13118</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Macul</t>
+        </is>
+      </c>
+      <c r="C210">
+        <v>39.3710970537462</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>13104</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Conchalí</t>
+        </is>
+      </c>
+      <c r="C211">
+        <v>39.0449250082952</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>13126</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Quinta Normal</t>
+        </is>
+      </c>
+      <c r="C212">
+        <v>38.7916290700212</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>13117</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Lo Prado</t>
+        </is>
+      </c>
+      <c r="C213">
+        <v>38.7635871230224</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>13601</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Talagante</t>
+        </is>
+      </c>
+      <c r="C214">
+        <v>38.729830851976</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>13502</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Alhué</t>
+        </is>
+      </c>
+      <c r="C215">
+        <v>38.6516279748868</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>13107</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Huechuraba</t>
+        </is>
+      </c>
+      <c r="C216">
+        <v>38.6136243956149</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>13132</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Vitacura</t>
+        </is>
+      </c>
+      <c r="C217">
+        <v>38.4223671610115</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>13404</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Paine</t>
+        </is>
+      </c>
+      <c r="C218">
+        <v>38.4071177160735</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>13128</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Renca</t>
+        </is>
+      </c>
+      <c r="C219">
+        <v>38.3948053037932</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>13103</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Cerro Navia</t>
+        </is>
+      </c>
+      <c r="C220">
+        <v>38.3663670617563</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>13129</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>San Joaquín</t>
+        </is>
+      </c>
+      <c r="C221">
+        <v>38.1839090964479</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>13603</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Isla de Maipo</t>
+        </is>
+      </c>
+      <c r="C222">
+        <v>38.1076766797272</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>13101</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Santiago</t>
+        </is>
+      </c>
+      <c r="C223">
+        <v>37.9622843426833</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>13125</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Quilicura</t>
+        </is>
+      </c>
+      <c r="C224">
+        <v>37.9530603168086</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>13103</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Cerro Navia</t>
+        </is>
+      </c>
+      <c r="C225">
+        <v>37.9050806728459</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>13116</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Lo Espejo</t>
+        </is>
+      </c>
+      <c r="C226">
+        <v>37.8366868944959</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>13302</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Lampa</t>
+        </is>
+      </c>
+      <c r="C227">
+        <v>37.6958234135732</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>13113</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>La Reina</t>
+        </is>
+      </c>
+      <c r="C228">
+        <v>37.6880324413563</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>13104</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Conchalí</t>
+        </is>
+      </c>
+      <c r="C229">
+        <v>37.5256489176157</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>13116</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Lo Espejo</t>
+        </is>
+      </c>
+      <c r="C230">
+        <v>37.248023715415</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>13602</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>El Monte</t>
+        </is>
+      </c>
+      <c r="C231">
+        <v>37.1882967477147</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>13502</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Alhué</t>
+        </is>
+      </c>
+      <c r="C232">
+        <v>37.1443675509419</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>13109</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>La Cisterna</t>
+        </is>
+      </c>
+      <c r="C233">
+        <v>37.1212978469802</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>13604</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Padre Hurtado</t>
+        </is>
+      </c>
+      <c r="C234">
+        <v>36.9880063362752</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>13402</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Buin</t>
+        </is>
+      </c>
+      <c r="C235">
+        <v>36.9550672958526</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>13122</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Peñalolén</t>
+        </is>
+      </c>
+      <c r="C236">
+        <v>36.8682505052065</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>13118</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Macul</t>
+        </is>
+      </c>
+      <c r="C237">
+        <v>36.7935737889334</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>13117</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Lo Prado</t>
+        </is>
+      </c>
+      <c r="C238">
+        <v>36.7014157014157</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>13127</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Recoleta</t>
+        </is>
+      </c>
+      <c r="C239">
+        <v>36.6647474165884</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>13124</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Pudahuel</t>
+        </is>
+      </c>
+      <c r="C240">
+        <v>36.4672966404873</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>13111</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>La Granja</t>
+        </is>
+      </c>
+      <c r="C241">
+        <v>36.4629778764249</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>13119</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Maipú</t>
+        </is>
+      </c>
+      <c r="C242">
+        <v>36.4034889262939</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>13105</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>El Bosque</t>
+        </is>
+      </c>
+      <c r="C243">
+        <v>36.3576761635898</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>13110</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>La Florida</t>
+        </is>
+      </c>
+      <c r="C244">
+        <v>36.3270456084827</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>13109</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>La Cisterna</t>
+        </is>
+      </c>
+      <c r="C245">
+        <v>36.3225367721136</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>13129</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>San Joaquín</t>
+        </is>
+      </c>
+      <c r="C246">
+        <v>36.2953973390867</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>13604</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Padre Hurtado</t>
+        </is>
+      </c>
+      <c r="C247">
+        <v>36.2951935800572</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>13101</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Santiago</t>
+        </is>
+      </c>
+      <c r="C248">
+        <v>36.2605580277233</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>13124</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Pudahuel</t>
+        </is>
+      </c>
+      <c r="C249">
+        <v>36.2427667457641</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>13112</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>La Pintana</t>
+        </is>
+      </c>
+      <c r="C250">
+        <v>36.0218406407262</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>13102</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Cerrillos</t>
+        </is>
+      </c>
+      <c r="C251">
+        <v>35.9399868017546</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>13120</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Ñuñoa</t>
+        </is>
+      </c>
+      <c r="C252">
+        <v>35.8274280003634</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>13201</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Puente Alto</t>
+        </is>
+      </c>
+      <c r="C253">
+        <v>35.8147748543371</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>13123</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Providencia</t>
+        </is>
+      </c>
+      <c r="C254">
+        <v>35.7660363366704</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>13131</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>San Ramón</t>
+        </is>
+      </c>
+      <c r="C255">
+        <v>35.6509139346636</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>13203</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>San José de Maipo</t>
+        </is>
+      </c>
+      <c r="C256">
+        <v>35.6471066116735</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>13131</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>San Ramón</t>
+        </is>
+      </c>
+      <c r="C257">
+        <v>35.6423564901074</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>13501</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Melipilla</t>
+        </is>
+      </c>
+      <c r="C258">
+        <v>35.5083465257172</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>13127</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Recoleta</t>
+        </is>
+      </c>
+      <c r="C259">
+        <v>35.4910868394526</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>13121</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Pedro Aguirre Cerda</t>
+        </is>
+      </c>
+      <c r="C260">
+        <v>35.4562726892324</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>13403</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Calera de Tango</t>
+        </is>
+      </c>
+      <c r="C261">
+        <v>35.4094888089222</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>13401</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>San Bernardo</t>
+        </is>
+      </c>
+      <c r="C262">
+        <v>35.3486691557268</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>13111</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>La Granja</t>
+        </is>
+      </c>
+      <c r="C263">
+        <v>35.096614552567</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>13501</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Melipilla</t>
+        </is>
+      </c>
+      <c r="C264">
+        <v>35.0814203648182</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>13503</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>Curacaví</t>
+        </is>
+      </c>
+      <c r="C265">
+        <v>35.0462871882309</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>13110</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>La Florida</t>
+        </is>
+      </c>
+      <c r="C266">
+        <v>35.0361619195766</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>13112</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>La Pintana</t>
+        </is>
+      </c>
+      <c r="C267">
+        <v>34.9636254777488</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>13504</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>María Pinto</t>
+        </is>
+      </c>
+      <c r="C268">
+        <v>34.9475045648204</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>13119</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Maipú</t>
+        </is>
+      </c>
+      <c r="C269">
+        <v>34.9178910300915</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>13102</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>Cerrillos</t>
+        </is>
+      </c>
+      <c r="C270">
+        <v>34.9113720398544</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>13121</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>Pedro Aguirre Cerda</t>
+        </is>
+      </c>
+      <c r="C271">
+        <v>34.7639484978541</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>13128</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>Renca</t>
+        </is>
+      </c>
+      <c r="C272">
+        <v>34.6631463359494</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>13302</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>Lampa</t>
+        </is>
+      </c>
+      <c r="C273">
+        <v>34.616209981357</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>13105</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>El Bosque</t>
+        </is>
+      </c>
+      <c r="C274">
+        <v>34.4794977670835</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>13201</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>Puente Alto</t>
+        </is>
+      </c>
+      <c r="C275">
+        <v>34.4490954422949</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>13401</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>San Bernardo</t>
+        </is>
+      </c>
+      <c r="C276">
+        <v>33.7738602303202</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>13104</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>Conchalí</t>
+        </is>
+      </c>
+      <c r="C277">
+        <v>33.7395561705072</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>13402</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>Buin</t>
+        </is>
+      </c>
+      <c r="C278">
+        <v>33.6909270896101</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>13129</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>San Joaquín</t>
+        </is>
+      </c>
+      <c r="C279">
+        <v>33.3635563117519</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>13601</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>Talagante</t>
+        </is>
+      </c>
+      <c r="C280">
+        <v>33.351846508944</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>13117</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>Lo Prado</t>
+        </is>
+      </c>
+      <c r="C281">
+        <v>33.1988302723638</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>13122</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>Peñalolén</t>
+        </is>
+      </c>
+      <c r="C282">
+        <v>33.1948604460385</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>13505</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>San Pedro</t>
+        </is>
+      </c>
+      <c r="C283">
+        <v>33.1848357791754</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>13202</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>Pirque</t>
+        </is>
+      </c>
+      <c r="C284">
+        <v>33.1494451975699</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>13601</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>Talagante</t>
+        </is>
+      </c>
+      <c r="C285">
+        <v>33.0153440869728</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>13605</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>Peñaflor</t>
+        </is>
+      </c>
+      <c r="C286">
+        <v>32.9750626973613</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>13602</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>El Monte</t>
+        </is>
+      </c>
+      <c r="C287">
+        <v>32.7993000241371</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>13404</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>Paine</t>
+        </is>
+      </c>
+      <c r="C288">
+        <v>32.6969129839813</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>13403</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>Calera de Tango</t>
+        </is>
+      </c>
+      <c r="C289">
+        <v>32.6048681720146</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>13603</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>Isla de Maipo</t>
+        </is>
+      </c>
+      <c r="C290">
+        <v>32.4172212636595</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>13404</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>Paine</t>
+        </is>
+      </c>
+      <c r="C291">
+        <v>32.3563236498834</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>13605</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>Peñaflor</t>
+        </is>
+      </c>
+      <c r="C292">
+        <v>32.2584062719019</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>13601</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>Talagante</t>
+        </is>
+      </c>
+      <c r="C293">
+        <v>32.2481622931296</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>13202</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>Pirque</t>
+        </is>
+      </c>
+      <c r="C294">
+        <v>32.0482321112044</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>13103</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>Cerro Navia</t>
+        </is>
+      </c>
+      <c r="C295">
+        <v>32.0269594897745</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>13601</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>Talagante</t>
+        </is>
+      </c>
+      <c r="C296">
+        <v>31.8522275503094</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>13504</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>María Pinto</t>
+        </is>
+      </c>
+      <c r="C297">
+        <v>31.8140112262522</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>13501</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>Melipilla</t>
+        </is>
+      </c>
+      <c r="C298">
+        <v>31.7655723905724</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>13114</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>Las Condes</t>
+        </is>
+      </c>
+      <c r="C299">
+        <v>31.6623420751861</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>13501</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>Melipilla</t>
+        </is>
+      </c>
+      <c r="C300">
+        <v>31.6175439416604</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>13505</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>San Pedro</t>
+        </is>
+      </c>
+      <c r="C301">
+        <v>31.487895716946</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>13203</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>San José de Maipo</t>
+        </is>
+      </c>
+      <c r="C302">
+        <v>31.3666537350748</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>13107</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>Huechuraba</t>
+        </is>
+      </c>
+      <c r="C303">
+        <v>31.2185285341291</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>13301</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>Colina</t>
+        </is>
+      </c>
+      <c r="C304">
+        <v>31.2046857211337</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>13503</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>Curacaví</t>
+        </is>
+      </c>
+      <c r="C305">
+        <v>31.1715858832025</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>13602</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>El Monte</t>
+        </is>
+      </c>
+      <c r="C306">
+        <v>30.7949952077343</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>13603</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>Isla de Maipo</t>
+        </is>
+      </c>
+      <c r="C307">
+        <v>30.4795523480807</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>13111</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>La Granja</t>
+        </is>
+      </c>
+      <c r="C308">
+        <v>30.4703982707516</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>13503</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>Curacaví</t>
+        </is>
+      </c>
+      <c r="C309">
+        <v>30.4662273476112</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>13105</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>El Bosque</t>
+        </is>
+      </c>
+      <c r="C310">
+        <v>30.2518096783384</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>13502</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>Alhué</t>
+        </is>
+      </c>
+      <c r="C311">
+        <v>29.9041189707465</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>13121</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>Pedro Aguirre Cerda</t>
+        </is>
+      </c>
+      <c r="C312">
+        <v>29.6524085978453</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>13131</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>San Ramón</t>
+        </is>
+      </c>
+      <c r="C313">
+        <v>29.3725495461625</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>13112</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>La Pintana</t>
+        </is>
+      </c>
+      <c r="C314">
+        <v>29.3320549267822</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>13504</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>María Pinto</t>
+        </is>
+      </c>
+      <c r="C315">
+        <v>29.2381552022666</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>13501</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>Melipilla</t>
+        </is>
+      </c>
+      <c r="C316">
+        <v>29.0518121490556</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>13501</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>Melipilla</t>
+        </is>
+      </c>
+      <c r="C317">
+        <v>29.0060771907137</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>13116</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>Lo Espejo</t>
+        </is>
+      </c>
+      <c r="C318">
+        <v>28.9123015873016</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>13505</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>San Pedro</t>
+        </is>
+      </c>
+      <c r="C319">
         <v>26.9086826347305</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>13203</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>San José de Maipo</t>
+        </is>
+      </c>
+      <c r="C320">
+        <v>26.7500445871232</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>13505</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>San Pedro</t>
+        </is>
+      </c>
+      <c r="C321">
+        <v>26.2314276485788</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>13113</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>La Reina</t>
+        </is>
+      </c>
+      <c r="C322">
+        <v>25.5976249975785</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>13132</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>Vitacura</t>
+        </is>
+      </c>
+      <c r="C323">
+        <v>25.4793607066334</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>13115</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>Lo Barnechea</t>
+        </is>
+      </c>
+      <c r="C324">
+        <v>25.3381419148018</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>13505</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>San Pedro</t>
+        </is>
+      </c>
+      <c r="C325">
+        <v>22.040072859745</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>13115</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>Lo Barnechea</t>
+        </is>
+      </c>
+      <c r="C326">
+        <v>21.686706746827</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>13125</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>Quilicura</t>
+        </is>
+      </c>
+      <c r="C327">
+        <v>18.8839018551765</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>13403</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>Calera de Tango</t>
+        </is>
+      </c>
+      <c r="C328">
+        <v>17.8156104001625</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>13101</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>Santiago</t>
+        </is>
+      </c>
+      <c r="C329">
+        <v>17.1759301581497</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>13201</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>Puente Alto</t>
+        </is>
+      </c>
+      <c r="C330">
+        <v>16.835358297369</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>13301</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>Colina</t>
+        </is>
+      </c>
+      <c r="C331">
+        <v>15.9972979611889</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>13202</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>Pirque</t>
+        </is>
+      </c>
+      <c r="C332">
+        <v>15.978272142709</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>13113</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>La Reina</t>
+        </is>
+      </c>
+      <c r="C333">
+        <v>15.960016100899</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>13119</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>Maipú</t>
+        </is>
+      </c>
+      <c r="C334">
+        <v>15.889700955615</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>13124</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>Pudahuel</t>
+        </is>
+      </c>
+      <c r="C335">
+        <v>15.6208105384993</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>13132</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>Vitacura</t>
+        </is>
+      </c>
+      <c r="C336">
+        <v>15.5393239074953</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>13123</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>Providencia</t>
+        </is>
+      </c>
+      <c r="C337">
+        <v>15.4040031474378</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>13302</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>Lampa</t>
+        </is>
+      </c>
+      <c r="C338">
+        <v>15.3199421745416</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>13114</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>Las Condes</t>
+        </is>
+      </c>
+      <c r="C339">
+        <v>15.3062885813085</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>13122</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>Peñalolén</t>
+        </is>
+      </c>
+      <c r="C340">
+        <v>14.9072832886506</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>13130</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>San Miguel</t>
+        </is>
+      </c>
+      <c r="C341">
+        <v>14.8730607423923</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>13108</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>Independencia</t>
+        </is>
+      </c>
+      <c r="C342">
+        <v>14.7423403091232</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>13402</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>Buin</t>
+        </is>
+      </c>
+      <c r="C343">
+        <v>14.7030023006864</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>13601</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>Talagante</t>
+        </is>
+      </c>
+      <c r="C344">
+        <v>14.6841996982581</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>13401</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>San Bernardo</t>
+        </is>
+      </c>
+      <c r="C345">
+        <v>14.4386472866711</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>13203</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>San José de Maipo</t>
+        </is>
+      </c>
+      <c r="C346">
+        <v>14.4353707828095</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>13107</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>Huechuraba</t>
+        </is>
+      </c>
+      <c r="C347">
+        <v>14.4157354242555</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>13101</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>Santiago</t>
+        </is>
+      </c>
+      <c r="C348">
+        <v>14.3719453896813</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>13120</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>Ñuñoa</t>
+        </is>
+      </c>
+      <c r="C349">
+        <v>14.3489440413033</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>13604</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>Padre Hurtado</t>
+        </is>
+      </c>
+      <c r="C350">
+        <v>13.9238686677017</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>13601</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>Talagante</t>
+        </is>
+      </c>
+      <c r="C351">
+        <v>13.90676910299</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>13603</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>Isla de Maipo</t>
+        </is>
+      </c>
+      <c r="C352">
+        <v>13.7922305072264</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>13126</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>Quinta Normal</t>
+        </is>
+      </c>
+      <c r="C353">
+        <v>13.7250498027421</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>13106</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>Estación Central</t>
+        </is>
+      </c>
+      <c r="C354">
+        <v>13.7239725095264</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>13605</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>Peñaflor</t>
+        </is>
+      </c>
+      <c r="C355">
+        <v>13.6174120939997</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>13111</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>La Granja</t>
+        </is>
+      </c>
+      <c r="C356">
+        <v>13.3891608221313</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>13102</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>Cerrillos</t>
+        </is>
+      </c>
+      <c r="C357">
+        <v>13.3659023534394</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>13128</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>Renca</t>
+        </is>
+      </c>
+      <c r="C358">
+        <v>13.3566819020723</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>13112</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>La Pintana</t>
+        </is>
+      </c>
+      <c r="C359">
+        <v>13.2917096448181</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>13404</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>Paine</t>
+        </is>
+      </c>
+      <c r="C360">
+        <v>13.2440903435735</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>13110</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>La Florida</t>
+        </is>
+      </c>
+      <c r="C361">
+        <v>13.2061901046356</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>13602</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>El Monte</t>
+        </is>
+      </c>
+      <c r="C362">
+        <v>13.1118800461361</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>13118</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>Macul</t>
+        </is>
+      </c>
+      <c r="C363">
+        <v>13.0957377354971</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>13116</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>Lo Espejo</t>
+        </is>
+      </c>
+      <c r="C364">
+        <v>12.8997333826498</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>13127</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>Recoleta</t>
+        </is>
+      </c>
+      <c r="C365">
+        <v>12.8238406380842</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>13104</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>Conchalí</t>
+        </is>
+      </c>
+      <c r="C366">
+        <v>12.4566699236925</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>13109</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>La Cisterna</t>
+        </is>
+      </c>
+      <c r="C367">
+        <v>12.3642952808635</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>13103</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>Cerro Navia</t>
+        </is>
+      </c>
+      <c r="C368">
+        <v>12.0513748191027</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>13105</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>El Bosque</t>
+        </is>
+      </c>
+      <c r="C369">
+        <v>12.0114693267794</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>13502</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>Alhué</t>
+        </is>
+      </c>
+      <c r="C370">
+        <v>11.947601010101</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>13501</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>Melipilla</t>
+        </is>
+      </c>
+      <c r="C371">
+        <v>11.8968719274608</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>13503</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>Curacaví</t>
+        </is>
+      </c>
+      <c r="C372">
+        <v>11.8830826075482</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>13121</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>Pedro Aguirre Cerda</t>
+        </is>
+      </c>
+      <c r="C373">
+        <v>11.8161638647936</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>13129</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>San Joaquín</t>
+        </is>
+      </c>
+      <c r="C374">
+        <v>11.6990187713311</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>13117</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>Lo Prado</t>
+        </is>
+      </c>
+      <c r="C375">
+        <v>11.670682351459</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>13501</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>Melipilla</t>
+        </is>
+      </c>
+      <c r="C376">
+        <v>11.6405764984165</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>13504</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>María Pinto</t>
+        </is>
+      </c>
+      <c r="C377">
+        <v>11.5758658330852</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>13131</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>San Ramón</t>
+        </is>
+      </c>
+      <c r="C378">
+        <v>11.1229650703335</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>13505</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>San Pedro</t>
+        </is>
+      </c>
+      <c r="C379">
+        <v>7.88501026694045</v>
       </c>
     </row>
   </sheetData>
